--- a/CHAMADA.xlsx
+++ b/CHAMADA.xlsx
@@ -20,7 +20,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
+  <si>
+    <t xml:space="preserve">29-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-09</t>
+  </si>
   <si>
     <t xml:space="preserve">Adriana Oleiro Faria</t>
   </si>
@@ -344,7 +353,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.31"/>
@@ -352,23 +361,22 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.4"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="n">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
         <v>180140</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>163736</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -376,219 +384,233 @@
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>136667</v>
+        <v>163736</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
-        <v>153801</v>
+        <v>136667</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
-        <v>156292</v>
+        <v>153801</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
-        <v>153791</v>
+        <v>156292</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>2</v>
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
-        <v>176868</v>
+        <v>153791</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
-        <v>174127</v>
+        <v>176868</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
-        <v>153792</v>
+        <v>174127</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
-        <v>138768</v>
+        <v>153792</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>2</v>
+        <v>21</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
-        <v>153795</v>
+        <v>138768</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
-        <v>153797</v>
+        <v>153795</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
-        <v>151182</v>
+        <v>153797</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>2</v>
+        <v>27</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
-        <v>157230</v>
+        <v>151182</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>2</v>
+        <v>29</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
-        <v>156289</v>
+        <v>157230</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
-        <v>117206</v>
+        <v>156289</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
-        <v>147556</v>
+        <v>117206</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="0" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
+        <v>147556</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
         <v>174131</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="n">
+      <c r="B19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="n">
         <v>133423</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>37</v>
+      <c r="B20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/CHAMADA.xlsx
+++ b/CHAMADA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="41">
   <si>
     <t xml:space="preserve">29-08</t>
   </si>
@@ -367,10 +367,10 @@
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -423,6 +423,9 @@
       <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -437,6 +440,9 @@
       <c r="D6" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -451,6 +457,9 @@
       <c r="D7" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -487,6 +496,9 @@
       <c r="D10" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="F10" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -501,6 +513,9 @@
       <c r="D11" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="F11" s="0" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
@@ -512,6 +527,9 @@
       <c r="C12" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="F12" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
@@ -526,6 +544,9 @@
       <c r="D13" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="F13" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -540,6 +561,9 @@
       <c r="D14" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="F14" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
@@ -554,6 +578,9 @@
       <c r="D15" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="F15" s="0" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
@@ -564,6 +591,9 @@
       </c>
       <c r="C16" s="2" t="s">
         <v>33</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/CHAMADA.xlsx
+++ b/CHAMADA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="42">
   <si>
     <t xml:space="preserve">29-08</t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t xml:space="preserve">12-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26-09</t>
   </si>
   <si>
     <t xml:space="preserve">Adriana Oleiro Faria</t>
@@ -149,8 +152,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -217,7 +221,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -228,6 +232,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -353,7 +361,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.31"/>
@@ -373,19 +381,25 @@
       <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="G1" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>180140</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -393,10 +407,10 @@
         <v>163736</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -404,13 +418,16 @@
         <v>136667</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -418,13 +435,16 @@
         <v>153801</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -432,16 +452,16 @@
         <v>156292</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -449,16 +469,16 @@
         <v>153791</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -466,10 +486,10 @@
         <v>176868</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -477,10 +497,10 @@
         <v>174127</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -488,16 +508,19 @@
         <v>153792</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -505,16 +528,19 @@
         <v>138768</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -522,13 +548,13 @@
         <v>153795</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -536,16 +562,16 @@
         <v>153797</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -553,16 +579,19 @@
         <v>151182</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -570,16 +599,19 @@
         <v>157230</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -587,13 +619,13 @@
         <v>156289</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="0" t="s">
-        <v>5</v>
+        <v>34</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -601,10 +633,10 @@
         <v>117206</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -612,13 +644,16 @@
         <v>147556</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -626,10 +661,10 @@
         <v>174131</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -637,10 +672,10 @@
         <v>133423</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/CHAMADA.xlsx
+++ b/CHAMADA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="43">
   <si>
     <t xml:space="preserve">29-08</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t xml:space="preserve">26-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03-10</t>
   </si>
   <si>
     <t xml:space="preserve">Adriana Oleiro Faria</t>
@@ -361,7 +364,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.31"/>
@@ -384,22 +387,28 @@
       <c r="G1" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="H1" s="0" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>180140</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -407,10 +416,10 @@
         <v>163736</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -418,16 +427,19 @@
         <v>136667</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -435,16 +447,16 @@
         <v>153801</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -452,16 +464,16 @@
         <v>156292</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -469,16 +481,19 @@
         <v>153791</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -486,10 +501,10 @@
         <v>176868</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -497,10 +512,10 @@
         <v>174127</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -508,19 +523,19 @@
         <v>153792</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -528,19 +543,19 @@
         <v>138768</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G11" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -548,13 +563,13 @@
         <v>153795</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -562,16 +577,16 @@
         <v>153797</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -579,19 +594,22 @@
         <v>151182</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="H14" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -599,19 +617,22 @@
         <v>157230</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -619,13 +640,13 @@
         <v>156289</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -633,10 +654,10 @@
         <v>117206</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -644,16 +665,16 @@
         <v>147556</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -661,10 +682,10 @@
         <v>174131</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -672,10 +693,10 @@
         <v>133423</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/CHAMADA.xlsx
+++ b/CHAMADA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="44">
   <si>
     <t xml:space="preserve">29-08</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t xml:space="preserve">03-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-10</t>
   </si>
   <si>
     <t xml:space="preserve">Adriana Oleiro Faria</t>
@@ -364,7 +367,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.31"/>
@@ -387,8 +390,11 @@
       <c r="G1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -396,19 +402,22 @@
         <v>180140</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -416,10 +425,10 @@
         <v>163736</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -427,19 +436,22 @@
         <v>136667</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -447,16 +459,19 @@
         <v>153801</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -464,16 +479,22 @@
         <v>156292</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -481,19 +502,22 @@
         <v>153791</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -501,10 +525,10 @@
         <v>176868</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -512,10 +536,10 @@
         <v>174127</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -523,19 +547,22 @@
         <v>153792</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -543,19 +570,19 @@
         <v>138768</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -563,13 +590,16 @@
         <v>153795</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="I12" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -577,16 +607,19 @@
         <v>153797</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="I13" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -594,22 +627,25 @@
         <v>151182</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H14" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -617,22 +653,25 @@
         <v>157230</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H15" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -640,13 +679,19 @@
         <v>156289</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="H16" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -654,10 +699,10 @@
         <v>117206</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -665,16 +710,19 @@
         <v>147556</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="I18" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -682,10 +730,10 @@
         <v>174131</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -693,10 +741,10 @@
         <v>133423</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/CHAMADA.xlsx
+++ b/CHAMADA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="45">
   <si>
     <t xml:space="preserve">29-08</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t xml:space="preserve">10-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17-10</t>
   </si>
   <si>
     <t xml:space="preserve">Adriana Oleiro Faria</t>
@@ -367,12 +370,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="7.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="7.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="6.31"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -396,28 +405,37 @@
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>180140</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -425,10 +443,10 @@
         <v>163736</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -436,22 +454,28 @@
         <v>136667</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -459,19 +483,25 @@
         <v>153801</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -479,22 +509,25 @@
         <v>156292</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -502,22 +535,28 @@
         <v>153791</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="J7" s="0" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -525,10 +564,10 @@
         <v>176868</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -536,10 +575,10 @@
         <v>174127</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -547,22 +586,28 @@
         <v>153792</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -570,19 +615,22 @@
         <v>138768</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -590,16 +638,22 @@
         <v>153795</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="0" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -607,19 +661,22 @@
         <v>153797</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I13" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -627,25 +684,28 @@
         <v>151182</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -653,25 +713,31 @@
         <v>157230</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="J15" s="0" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -679,19 +745,25 @@
         <v>156289</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H16" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="I16" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -699,10 +771,13 @@
         <v>117206</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -710,19 +785,22 @@
         <v>147556</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I18" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -730,10 +808,10 @@
         <v>174131</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -741,10 +819,10 @@
         <v>133423</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/CHAMADA.xlsx
+++ b/CHAMADA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="46">
   <si>
     <t xml:space="preserve">29-08</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t xml:space="preserve">17-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31-10</t>
   </si>
   <si>
     <t xml:space="preserve">Adriana Oleiro Faria</t>
@@ -370,7 +373,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.31"/>
@@ -382,6 +385,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="7.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="6.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="5.91"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -408,34 +412,37 @@
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>180140</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -443,10 +450,10 @@
         <v>163736</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -454,28 +461,28 @@
         <v>136667</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -483,25 +490,28 @@
         <v>153801</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -509,25 +519,28 @@
         <v>156292</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -535,28 +548,31 @@
         <v>153791</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -564,10 +580,10 @@
         <v>176868</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -575,10 +591,10 @@
         <v>174127</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -586,28 +602,31 @@
         <v>153792</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -615,22 +634,22 @@
         <v>138768</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -638,22 +657,22 @@
         <v>153795</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -661,22 +680,25 @@
         <v>153797</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -684,28 +706,31 @@
         <v>151182</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -713,31 +738,31 @@
         <v>157230</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -745,25 +770,28 @@
         <v>156289</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -771,13 +799,13 @@
         <v>117206</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -785,22 +813,28 @@
         <v>147556</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K18" s="0" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -808,10 +842,10 @@
         <v>174131</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -819,10 +853,10 @@
         <v>133423</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/CHAMADA.xlsx
+++ b/CHAMADA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="47">
   <si>
     <t xml:space="preserve">29-08</t>
   </si>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t xml:space="preserve">31-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14-11</t>
   </si>
   <si>
     <t xml:space="preserve">Adriana Oleiro Faria</t>
@@ -373,7 +376,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.31"/>
@@ -415,34 +418,37 @@
       <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="L1" s="0" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>180140</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -450,10 +456,10 @@
         <v>163736</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -461,28 +467,28 @@
         <v>136667</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -490,28 +496,31 @@
         <v>153801</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="L5" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -519,28 +528,28 @@
         <v>156292</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -548,31 +557,34 @@
         <v>153791</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="L7" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -580,10 +592,10 @@
         <v>176868</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -591,10 +603,10 @@
         <v>174127</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -602,31 +614,34 @@
         <v>153792</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="L10" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -634,22 +649,25 @@
         <v>138768</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="L11" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -657,22 +675,22 @@
         <v>153795</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -680,25 +698,28 @@
         <v>153797</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="L13" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -706,31 +727,31 @@
         <v>151182</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -738,31 +759,31 @@
         <v>157230</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -770,28 +791,31 @@
         <v>156289</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="L16" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -799,13 +823,13 @@
         <v>117206</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -813,28 +837,28 @@
         <v>147556</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K18" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -842,10 +866,10 @@
         <v>174131</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -853,10 +877,10 @@
         <v>133423</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/CHAMADA.xlsx
+++ b/CHAMADA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="48">
   <si>
     <t xml:space="preserve">29-08</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t xml:space="preserve">14-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28-11</t>
   </si>
   <si>
     <t xml:space="preserve">Adriana Oleiro Faria</t>
@@ -376,7 +379,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.31"/>
@@ -418,8 +421,11 @@
       <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -427,28 +433,28 @@
         <v>180140</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -456,10 +462,10 @@
         <v>163736</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -467,28 +473,28 @@
         <v>136667</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -496,31 +502,34 @@
         <v>153801</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L5" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -528,28 +537,31 @@
         <v>156292</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -557,34 +569,34 @@
         <v>153791</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L7" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -592,10 +604,10 @@
         <v>176868</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -603,10 +615,10 @@
         <v>174127</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -614,34 +626,37 @@
         <v>153792</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L10" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -649,25 +664,25 @@
         <v>138768</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L11" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -675,22 +690,22 @@
         <v>153795</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -698,28 +713,28 @@
         <v>153797</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L13" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -727,31 +742,34 @@
         <v>151182</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="M14" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -759,31 +777,34 @@
         <v>157230</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -791,31 +812,31 @@
         <v>156289</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L16" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -823,13 +844,13 @@
         <v>117206</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -837,28 +858,31 @@
         <v>147556</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="M18" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -866,10 +890,10 @@
         <v>174131</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -877,10 +901,10 @@
         <v>133423</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/CHAMADA.xlsx
+++ b/CHAMADA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="49">
   <si>
     <t xml:space="preserve">29-08</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t xml:space="preserve">28-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enviados</t>
   </si>
   <si>
     <t xml:space="preserve">Adriana Oleiro Faria</t>
@@ -379,53 +382,61 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="7.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="7.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="6.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="5.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="3.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="29.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="7.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="7.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="6.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="6.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="6.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="5.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="6.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="5.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="11.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2"/>
+      <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -433,28 +444,31 @@
         <v>180140</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -462,39 +476,43 @@
         <v>163736</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>136667</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -502,101 +520,106 @@
         <v>153801</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>12</v>
+      <c r="D5" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>156292</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
+      <c r="D6" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>153791</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>12</v>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -604,85 +627,91 @@
         <v>176868</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="D8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>174127</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="D9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>153792</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>12</v>
+      <c r="D10" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>138768</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>12</v>
+      <c r="D11" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -690,22 +719,25 @@
         <v>153795</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>12</v>
+      <c r="D12" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -713,28 +745,31 @@
         <v>153797</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>12</v>
+      <c r="D13" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -742,101 +777,106 @@
         <v>151182</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>12</v>
+      <c r="D14" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M14" s="0" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>157230</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>12</v>
+      <c r="D15" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>156289</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>12</v>
+      <c r="D16" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -844,68 +884,72 @@
         <v>117206</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="D17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>147556</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>12</v>
+      <c r="D18" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M18" s="0" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>174131</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="n">
         <v>133423</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="D20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O20" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
